--- a/quality_surveys/043_e_commerce_quality_control_application_form--quality_surveys.xlsx
+++ b/quality_surveys/043_e_commerce_quality_control_application_form--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'used'}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Used'}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'refurbished'}</t>
+          <t>refurbished</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Refurbished'}</t>
+          <t>Refurbished</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'shipped'}</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Shipped'}</t>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_shipped'}</t>
+          <t>not_shipped</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Shipped'}</t>
+          <t>Not Shipped</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'store'}</t>
+          <t>store</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Store'}</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'ups'}</t>
+          <t>ups</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'UPS'}</t>
+          <t>UPS</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'fedex'}</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'FedEx'}</t>
+          <t>FedEx</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'usps'}</t>
+          <t>usps</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'USPS'}</t>
+          <t>USPS</t>
         </is>
       </c>
     </row>
